--- a/salidas/empleo_Excel.xlsx
+++ b/salidas/empleo_Excel.xlsx
@@ -17,7 +17,7 @@
     <t xml:space="preserve">Código Región</t>
   </si>
   <si>
-    <t xml:space="preserve">region_name</t>
+    <t xml:space="preserve">Región de Chile</t>
   </si>
   <si>
     <t xml:space="preserve">I01_Agropecuario-silvícola y Pesca</t>
